--- a/AAII_Financials/Quarterly/RYAA.Y_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RYAA.Y_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>RYAA.Y</t>
   </si>
@@ -656,212 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5008700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2897000</v>
+      </c>
+      <c r="F8" s="3">
         <v>3773900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6429500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>5094100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2483000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3063700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5650100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3885200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2341000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2983000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5213700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3984000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2006700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2471000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3642900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2844100</v>
+      </c>
+      <c r="F9" s="3">
         <v>3065200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3486000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3358500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2502600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2483600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3184800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2922900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2272800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2541800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2855800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2687700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1811200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1910800</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1365800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>52900</v>
+      </c>
+      <c r="F10" s="3">
         <v>708700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2943600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1735500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-19600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>580100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2465300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>962400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>68200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>441100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2357900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1296300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>195600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>560200</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +904,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +950,14 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,20 +1000,26 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="F14" s="3">
         <v>99800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1010,52 +1050,64 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>476500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>414500</v>
+      </c>
+      <c r="F15" s="3">
         <v>383200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>403800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>403200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>319000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>302200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>350400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>335600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>256000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>291100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>300500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>300100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>279700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1121,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4351300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3576700</v>
+      </c>
+      <c r="F17" s="3">
         <v>3652700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4144900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4021500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3011700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3029900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3811200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3493400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2703700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3003900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3409500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3207500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2250400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2309200</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>657400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-679700</v>
+      </c>
+      <c r="F18" s="3">
         <v>121200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2284600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1072600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-528600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>33800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1838900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>391800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-362700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-20900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1804200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>776400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-243700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>161800</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,228 +1241,260 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F20" s="3">
         <v>3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>37300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>22600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-21600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-7500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>12100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-6400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-12400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-25500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-71900</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1136900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="F21" s="3">
         <v>501100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2691000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1438400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-232300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>357600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2184300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>734900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-118800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>276700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2104100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1089000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>61500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
+      <c r="E22" s="3">
+        <v>43600</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>71900</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>89500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>37700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>677400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-568100</v>
+      </c>
+      <c r="F23" s="3">
         <v>28600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2301300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1092400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-460700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>148800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1858200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>429400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-359500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1818200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>808600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-209800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-112100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>284500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>129500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-105900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-5100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>262000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>43700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-61900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-13400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>214400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>84900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-45000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1537,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>614300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-456000</v>
+      </c>
+      <c r="F26" s="3">
         <v>35700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2016800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>962900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-354700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>153800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1596300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>385700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-297600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>16400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1603700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>723700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-164800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>614300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-456000</v>
+      </c>
+      <c r="F27" s="3">
         <v>35700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2016800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>962900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-354700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>153800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1596300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>385700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-297600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>16400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1603700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>723700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-164800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1687,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1737,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1787,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1837,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-37300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-22600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>21600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>7500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-12100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>6400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>12400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>25500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>614300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-456000</v>
+      </c>
+      <c r="F33" s="3">
         <v>35700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2016800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>962900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-354700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>153800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1596300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>385700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-297600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>16400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1603700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>723700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-164800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1987,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>614300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-456000</v>
+      </c>
+      <c r="F35" s="3">
         <v>35700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2016800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>962900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-354700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>153800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1596300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>385700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-297600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>16400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1603700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>723700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-164800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2116,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,272 +2136,310 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2837700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3151600</v>
+      </c>
+      <c r="F41" s="3">
         <v>2808100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3477100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4243500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4175600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2848300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3263700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4237800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4181000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2783900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3451000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3225800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3910600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2436100</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>365200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>936700</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>863100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>108200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>447600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>563700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>256600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>419500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>386200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2039100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1147500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1893100</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>56200</v>
+      </c>
+      <c r="F43" s="3">
         <v>129600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>91200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>113800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>84600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>58600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>106000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>107700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>89700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>84600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>72300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>96700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>76100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>41500</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F44" s="3">
         <v>6200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>5900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>6900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3729000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2460400</v>
+      </c>
+      <c r="F45" s="3">
         <v>2072700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1920700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2348000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>102000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2097500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1632700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2065400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>377100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1439600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1777900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1121900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>317400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>594100</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7082300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8929900</v>
+      </c>
+      <c r="F46" s="3">
         <v>5053300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5528700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7601300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6495600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5033300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5462300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6987600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6286700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4757400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5714100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>6510500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6422600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5855500</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2263,105 +2473,123 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>1000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13137800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13284000</v>
+      </c>
+      <c r="F48" s="3">
         <v>13281300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>13179300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13082700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>11967400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>11431700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>12391500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>11908200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>11882100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>11934300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>11120800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>11300000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>10993000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>10548400</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>171900</v>
+        <v>167300</v>
       </c>
       <c r="E49" s="3">
-        <v>171800</v>
+        <v>168800</v>
       </c>
       <c r="F49" s="3">
         <v>171900</v>
       </c>
       <c r="G49" s="3">
+        <v>171800</v>
+      </c>
+      <c r="H49" s="3">
+        <v>171900</v>
+      </c>
+      <c r="I49" s="3">
         <v>158200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>151600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>163300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>156900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>157900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>161800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>155000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>159800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>159100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>156500</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2632,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2682,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>383800</v>
+      </c>
+      <c r="F52" s="3">
         <v>299200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>332000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>332500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>299500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>332700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>245100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>245800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>201200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>223700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>328600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>246200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>242800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>278500</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2782,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20750900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22769200</v>
+      </c>
+      <c r="F54" s="3">
         <v>18837600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>19229300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>21229600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>18922400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16951300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>18264300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19300700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18530200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>17083800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17324600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>18223800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>17824800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>16844000</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2856,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,272 +2876,310 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>814600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>703100</v>
+      </c>
+      <c r="F57" s="3">
         <v>560800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>683300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>675500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>758800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>658600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>985600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>936200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>854700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>893400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1039700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>915000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1157600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1254700</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1428100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1449000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1447700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2445300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>957700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>918700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1037500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>90500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>96500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>121600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>81300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>940700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1195000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2109100</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>173900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4198900</v>
+      </c>
+      <c r="F59" s="3">
         <v>788200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>806900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>778000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4068300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>373300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>563200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>129200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3392400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>255900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>142800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>560000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3519600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>167600</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8968800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9884500</v>
+      </c>
+      <c r="F60" s="3">
         <v>7584100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7745600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11513800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>8811900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5853800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6744900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7507700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6905400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4737000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4803600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7807800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8063500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6337000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>291600</v>
+      </c>
+      <c r="F61" s="3">
         <v>262400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>273500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>283400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1941900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1876400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2022000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2856500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2867000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2943300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2883400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3272100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3277200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3265600</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>175600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>171900</v>
+      </c>
+      <c r="F62" s="3">
         <v>214000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>247400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>315700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>155200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>199800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>307800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>124400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>152600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>254700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>184500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>200200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>175100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>230600</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3222,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3272,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3322,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9919800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11122200</v>
+      </c>
+      <c r="F66" s="3">
         <v>8527300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8705000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12536900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11316600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8492700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9612500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>10914800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10315500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8383100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8403500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>11508600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>11693700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10119300</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3396,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3442,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3492,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3542,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3592,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8166000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>7814500</v>
+      </c>
+      <c r="F72" s="3">
         <v>8862300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>9016000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>7449800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>6040400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>6757400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7402300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>6438800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6365100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>7040800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6729000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5286700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4541500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4629500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3692,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3742,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3792,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10831100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11647000</v>
+      </c>
+      <c r="F76" s="3">
         <v>10310300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10524200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8692700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7605800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8458600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8651800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8385800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8214700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8700700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8921100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6715200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6131000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6724700</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3892,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>614300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-456000</v>
+      </c>
+      <c r="F81" s="3">
         <v>35700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2016800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>962900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-354700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>153800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1596300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>385700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-297600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>16400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1603700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>723700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-164800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4021,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>403200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>319000</v>
+      </c>
+      <c r="F83" s="3">
         <v>302200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>350400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>335600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>256000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>291100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>300500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>300100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>279700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>227300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>222300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>236700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>210600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>220200</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4117,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4167,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4217,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4267,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4317,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1374800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2292900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-85500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>376500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1712500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2508100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-89700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>61500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1207200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2019900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-392100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>411500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1366400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2359800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-40300</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4391,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-542300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-524800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-380300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-575500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-731400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-496900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-210300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-433000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-537300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-494400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-385300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-552000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-699900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-396400</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4487,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4537,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1461500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-383400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>280300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1476900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-605100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>187900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-293800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-846200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-326000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-402900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1036500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2044800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>78000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>753200</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,41 +4611,43 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
+        <v>233600</v>
+      </c>
+      <c r="F96" s="3">
         <v>13700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>268700</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>259800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>11800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>207300</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>215200</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
@@ -4189,8 +4657,14 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4707,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4757,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4807,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1683400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-442200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-211500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1443300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-478000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-663500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-332900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-891400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-281200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-243500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-12200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1128800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-25200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-984200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-64400</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-51200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="F101" s="3">
         <v>53400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-23900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>5600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>13500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-12900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>4300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3">
         <v>-19700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-55000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>32300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>32600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>19400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-285200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>394000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-671400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-762400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-293600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1202000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-181200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1147600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>85400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1463800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-820100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>323600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-703600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1433900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>593500</v>
       </c>
     </row>
